--- a/jogos_2025-01-22.xlsx
+++ b/jogos_2025-01-22.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="U4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.88</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Y4" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['27', '42', '48']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45679.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.62</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['27', '42', '48']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45679.41666666666</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1174,10 +1174,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.8</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AJ6" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>7</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45679.41666666666</v>
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.13</v>
+        <v>1.72</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45679.58333333334</v>
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45679.58333333334</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
         <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.4</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.85</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['18', '37']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['19', '78']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45679.61458333334</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>3.25</v>
       </c>
       <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA20" t="n">
-        <v>3.55</v>
+        <v>2.26</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['18', '37']</t>
+          <t>['19', '78']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45679.61458333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="M24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA24" t="n">
         <v>3.75</v>
       </c>
-      <c r="N24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="AB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['11', '31', '34', '45', '45+2']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI24" t="n">
         <v>3.25</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['43', '83', '86']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45679.70833333334</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="O25" t="n">
-        <v>5.5</v>
-      </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>6.4</v>
+        <v>4.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['21', '45+9', '89']</t>
+          <t>['56', '60', '78', '90+3']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '53']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>2.65</v>
+        <v>1.46</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45679.70833333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="O26" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45679.70833333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>18</v>
+        <v>1.83</v>
       </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="P27" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>2.6</v>
       </c>
       <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.22</v>
       </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['2', '66', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>6</v>
-      </c>
       <c r="AI27" t="n">
-        <v>1.13</v>
+        <v>2.88</v>
       </c>
       <c r="AJ27" t="n">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45679.70833333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Vere United</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.15</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>8</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.33</v>
       </c>
-      <c r="P28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>15</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="AC28" t="n">
         <v>1.73</v>
       </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['23', '34', '48', '55', '77']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['-1', '-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.13</v>
+        <v>1.7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45679.70833333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="R29" t="n">
         <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>4.85</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['43', '83', '86']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['56', '60', '78', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['50', '53']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45679.70833333334</v>
@@ -4255,23 +4255,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="O30" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
         <v>1.22</v>
@@ -4305,10 +4305,10 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
@@ -4320,26 +4320,26 @@
         <v>6.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['2', '66', '90+1']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45679.70833333334</v>
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="N31" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="O31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>15</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.95</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['23', '34', '48', '55', '77']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45679.70833333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.2</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
         <v>4.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.49</v>
+        <v>6.8</v>
       </c>
       <c r="O32" t="n">
-        <v>6.5</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
         <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
@@ -4575,19 +4575,19 @@
         <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AC32" t="n">
         <v>1.91</v>
@@ -4597,25 +4597,25 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
       <c r="AG32" t="n">
-        <v>2.7</v>
+        <v>1.11</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.11</v>
+        <v>2.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.75</v>
+        <v>1.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45679.70833333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N33" t="n">
         <v>6.2</v>
       </c>
-      <c r="M33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.54</v>
-      </c>
       <c r="O33" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="P33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="AA33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['11', '31', '34', '45', '45+2']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45679.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vere United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="T34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.9</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['21', '45+9', '89']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI34" t="n">
         <v>3.25</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AJ34" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45679.70833333334</v>
